--- a/threagile/output/ai-ml/risks.xlsx
+++ b/threagile/output/ai-ml/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$37</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$76</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="394">
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
   <si>
     <t>Severity</t>
   </si>
   <si>
-    <t>Function</t>
-  </si>
-  <si>
     <t>Risk Category</t>
   </si>
   <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
     <t>Identified Risk</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
     <t>Check</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
     <t>Likelihood</t>
   </si>
   <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t/>
   </si>
   <si>
-    <t>39</t>
+    <t>21</t>
   </si>
   <si>
     <t>Exposed Default Credentials: MinIO Object Storage is tagged as intentional-misconfiguration and stores confidential data</t>
@@ -144,7 +144,7 @@
     <t>PostgreSQL Connection</t>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>SQL/NoSQL-Injection risk at API Server against database PostgreSQL Database via PostgreSQL Connection</t>
@@ -180,94 +180,361 @@
     <t>Likely</t>
   </si>
   <si>
+    <t>Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>CWE-306</t>
+  </si>
+  <si>
+    <t>AI/ML - LLM Inference Endpoint Internet-Accessible Without Authentication</t>
+  </si>
+  <si>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Inference Endpoint No Auth: LLM inference endpoint LLM Note Summarizer is internet-accessible without authentication</t>
+  </si>
+  <si>
+    <t>Require API-key, OAuth 2.0, or mTLS authentication on all LLM inference endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place the inference endpoint behind an API gateway with mandatory authentication (API key, OAuth 2.0 bearer token, or mTLS). Enforce authentication at the network layer so unauthenticated requests are rejected before reaching the model runtime. Implement per-caller rate limiting and quota enforcement alongside authentication. Tag the asset has-authentication once authentication controls are verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is authentication required on every path to the LLM inference endpoint? Are API keys rotated regularly and scoped to least-privilege?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-inference-endpoint-no-auth@llm-summarizer</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API key authentication is being added to the LiteLLM proxy. The development endpoint is publicly accessible for testing purposes only. Authentication enforcement and rate limiting (VAULT-140) are pre-launch requirements.
+</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>Security Team</t>
+  </si>
+  <si>
+    <t>VAULT-137</t>
+  </si>
+  <si>
+    <t>CWE-532</t>
+  </si>
+  <si>
+    <t>AI/ML - LLM Inference Endpoint Logging PII Without Sanitization</t>
+  </si>
+  <si>
+    <t>Inference Logs PII: LLM endpoint LLM Note Summarizer processes PII without log sanitization, creating uncontrolled PII copies in logs</t>
+  </si>
+  <si>
+    <t>Implement PII masking or redaction in all inference request and response log pipelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply a log sanitization layer that masks or redacts PII fields before they reach the log aggregation system. Use a PII detection library (Presidio, AWS Comprehend, Google DLP) to identify and redact personal data in prompt and response text. Configure inference logging to capture only metadata (latency, token counts, error codes) without full prompt content in production. Tag the asset has-log-sanitization once redaction controls are verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are all inference request and response logs scanned for PII before storage? Is PII masked or redacted in all log outputs accessible to engineering staff?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-inference-logs-pii@llm-summarizer</t>
+  </si>
+  <si>
+    <t>CWE-798</t>
+  </si>
+  <si>
+    <t>AI/ML - LLM Inference Endpoint With Custom Code and No Secrets Manager</t>
+  </si>
+  <si>
+    <t>LLM API Key Hardcoded Risk: LLM endpoint LLM Note Summarizer has custom code without a secrets manager, risking hardcoded credentials</t>
+  </si>
+  <si>
+    <t>Store all LLM API credentials in a dedicated secrets manager; never hard-code them in source or config files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store LLM API keys in a dedicated secrets manager (HashiCorp Vault, AWS Secrets Manager, GCP Secret Manager, Azure Key Vault). Inject credentials at runtime via environment variable injection from the secrets manager. Enable pre-commit hooks (detect-secrets, gitleaks) to prevent credential commits. Rotate any previously committed keys immediately. Tag the asset has-secrets-manager once key management is verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are all LLM API keys stored in a dedicated secrets manager rather than source code or env defaults? Are pre-commit secret-scanning hooks active on all repositories that contain LLM client code?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-llm-api-key-hardcoded@llm-summarizer</t>
+  </si>
+  <si>
+    <t>CWE-693</t>
+  </si>
+  <si>
+    <t>AI/ML - LLM Inference Endpoint Without Input Shield Against Adversarial Inputs</t>
+  </si>
+  <si>
+    <t>Adversarial Input No Shield: LLM endpoint LLM Note Summarizer has no input shielding layer, exposing it to prompt injection and jailbreak attacks</t>
+  </si>
+  <si>
+    <t>Deploy an input shield (content safety classifier or guardrail layer) in front of all LLM inference endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy a dedicated input safety classifier (e.g. Llama Guard, Azure Content Safety, OpenAI Moderation API, Rebuff) that screens all user inputs for prompt injection patterns, toxicity, jailbreak attempts, and policy violations before they reach the core model. Implement a deny-list for known jailbreak patterns and maintain it as a living artefact. Apply structured input parsing where possible to constrain the attack surface. Tag the asset has-input-shield once the shielding layer is verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a content safety classifier or guardrail model screening all inputs before they reach the LLM inference endpoint? Are known jailbreak and prompt injection patterns blocked at the input layer?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-adversarial-input-no-shield@llm-summarizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llama Guard integration is planned as an input/output shield for the LLM endpoint. Currently no adversarial prompt detection or content policy enforcement is in place. Pre-launch requirement tracked under VAULT-140.
+</t>
+  </si>
+  <si>
+    <t>VAULT-140</t>
+  </si>
+  <si>
+    <t>Denial of Service</t>
+  </si>
+  <si>
+    <t>CWE-770</t>
+  </si>
+  <si>
+    <t>AI/ML - LLM Inference Endpoint Without Rate Limiting</t>
+  </si>
+  <si>
+    <t>Inference Endpoint No Rate Limiting: LLM endpoint LLM Note Summarizer has no rate limiting, enabling prompt flooding and cost amplification</t>
+  </si>
+  <si>
+    <t>Configure per-caller token-per-minute and request-per-minute rate limits on all LLM endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement request-per-minute and tokens-per-minute rate limits at the API gateway layer in front of the inference endpoint. Apply per-caller quotas using API keys or authenticated identity. Set hard monthly budget caps at the inference provider level. Alert on anomalous usage patterns. Tag the asset has-rate-limiting once throttling policies are verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are per-caller request-per-minute and token-per-minute limits configured? Are hard monthly spend caps enforced at the provider or gateway level?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-inference-endpoint-no-rate-limiting@llm-summarizer</t>
+  </si>
+  <si>
+    <t>CWE-77</t>
+  </si>
+  <si>
+    <t>AI/ML - RAG Pipeline Without Input Validation Enabling Prompt Injection</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Prompt Injection via RAG: RAG pipeline Note RAG Pipeline lacks input validation enabling prompt injection through retrieved context</t>
+  </si>
+  <si>
+    <t>Implement input validation and prompt-injection detection on all RAG pipeline inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply input validation at the RAG pipeline ingress to detect and reject prompt injection patterns. Sanitize user inputs before embedding and retrieval steps. Use a dedicated prompt-injection detection model or guardrail layer (e.g. Llama Guard, Rebuff) before injecting retrieved content into the LLM context. Enforce strict output schemas and refuse to process instructions embedded in retrieved documents. Tag the asset has-input-validation once validation controls are verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is user input sanitized before it is used as a retrieval query? Are retrieved documents scanned for embedded prompt-injection instructions?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-prompt-injection-rag-context@rag-pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LangChain prompt injection guards (output parsers, system prompt isolation) are being evaluated. Interim mitigation: note content is truncated to 500 tokens before RAG injection. Full input validation (Llama Guard integration) is planned for Q3 2026.
+</t>
+  </si>
+  <si>
+    <t>VAULT-139</t>
+  </si>
+  <si>
+    <t>CWE-200</t>
+  </si>
+  <si>
+    <t>AI/ML - RAG Pipeline Without Retrieval Filtering</t>
+  </si>
+  <si>
+    <t>RAG No Retrieval Filtering: RAG pipeline Note RAG Pipeline injects retrieved documents without access-level filtering, enabling unauthorized disclosure</t>
+  </si>
+  <si>
+    <t>Enforce caller-identity-based document filtering before injecting retrieved content into LLM context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply pre-retrieval and post-retrieval access-control filters that match documents to the authenticated caller's entitlements. Store document-level ACL metadata in the vector store and enforce it server-side on every query. Alternatively, segment the vector store by access tier and route queries to the appropriate segment based on identity. Tag the asset has-retrieval-filtering once access filtering is verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is every retrieved document filtered against the caller's access entitlements before it is injected into the LLM context? Is retrieval filtering enforced server-side rather than relying on post-hoc output filtering?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-rag-no-retrieval-filtering@rag-pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retrieval filtering (relevance score threshold &gt; 0.7, max 5 chunks) is planned for the next sprint. Currently all vector store results are injected regardless of similarity score. This creates noise and increases prompt injection surface.
+</t>
+  </si>
+  <si>
+    <t>CWE-312</t>
+  </si>
+  <si>
+    <t>AI/ML - Vector Store Without Encryption at Rest</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Vector Store No Encryption: vector store VaultNote Vector Store persists embeddings without encryption at rest</t>
+  </si>
+  <si>
+    <t>Enable encryption at rest on all vector store volumes and index files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable volume-level or database-level encryption on the vector store using provider-managed or customer-managed keys (SSE-KMS, CMEK, LUKS). For self-hosted deployments (Qdrant, Weaviate, Milvus, Chroma), configure full-disk encryption on the underlying storage. Update the encryption field on the asset to transparent or higher once encryption is enabled.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is encryption at rest enabled on all vector store volumes and index files? Are customer-managed KMS keys used when the store contains confidential embeddings?
+</t>
+  </si>
+  <si>
+    <t>ai-ml-vector-store-no-encryption@vector-store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qdrant encryption at rest is available in the Enterprise version. OSS deployment will be migrated to Qdrant Cloud (managed) with SSE enabled, or wrapped in an encrypted volume. Tracked alongside RDS encryption work.
+</t>
+  </si>
+  <si>
+    <t>VAULT-138</t>
+  </si>
+  <si>
     <t>Lateral Movement</t>
   </si>
   <si>
-    <t>Architecture</t>
-  </si>
-  <si>
     <t>CWE-0</t>
   </si>
   <si>
     <t>Lateral Movement via Shared Runtime</t>
   </si>
   <si>
+    <t>PostgreSQL Database</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
+  </si>
+  <si>
+    <t>Runtime Isolation</t>
+  </si>
+  <si>
+    <t>Separate assets from different trust zones onto dedicated runtimes (separate node pools, dedicated VMs, distinct container namespaces with NetworkPolicy). Apply seccomp/AppArmor profiles and disable privilege escalation.</t>
+  </si>
+  <si>
+    <t>Are high-trust and low-trust assets co-located on the same shared runtime?</t>
+  </si>
+  <si>
+    <t>lateral-movement-shared-runtime@docker-host</t>
+  </si>
+  <si>
+    <t>Missing Authentication</t>
+  </si>
+  <si>
+    <t>HTTP to API Server</t>
+  </si>
+  <si>
+    <t>Missing Authentication covering communication link HTTP to API Server from Nginx Reverse Proxy to API Server</t>
+  </si>
+  <si>
+    <t>Authentication of Incoming Requests</t>
+  </si>
+  <si>
+    <t>Apply an authentication method to the technical asset. To protect highly sensitive data consider the use of two-factor authentication for human users.</t>
+  </si>
+  <si>
+    <t>missing-authentication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
+  </si>
+  <si>
+    <t>Route to ECS API</t>
+  </si>
+  <si>
+    <t>Missing Authentication covering communication link Route to ECS API from AWS API Gateway to API Server</t>
+  </si>
+  <si>
+    <t>missing-authentication@aws-api-gateway&gt;route-to-ecs-api@aws-api-gateway@api-server</t>
+  </si>
+  <si>
+    <t>Unlikely</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>CWE-1008</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening (AWS) risk at AWS Cloud: CIS Benchmark for AWS</t>
+  </si>
+  <si>
+    <t>Cloud Hardening</t>
+  </si>
+  <si>
+    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@aws-cloud@aws</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening risk at Docker Host</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@docker-host</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening risk at External CI/CD</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@external-cicd</t>
+  </si>
+  <si>
+    <t>Missing Content-Security-Policy Header on Web Entry Point</t>
+  </si>
+  <si>
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
-  </si>
-  <si>
-    <t>Runtime Isolation</t>
-  </si>
-  <si>
-    <t>Separate assets from different trust zones onto dedicated runtimes (separate node pools, dedicated VMs, distinct container namespaces with NetworkPolicy). Apply seccomp/AppArmor profiles and disable privilege escalation.</t>
-  </si>
-  <si>
-    <t>Are high-trust and low-trust assets co-located on the same shared runtime?</t>
-  </si>
-  <si>
-    <t>lateral-movement-shared-runtime@docker-host</t>
-  </si>
-  <si>
-    <t>Elevation of Privilege</t>
-  </si>
-  <si>
-    <t>CWE-306</t>
-  </si>
-  <si>
-    <t>Missing Authentication</t>
-  </si>
-  <si>
-    <t>HTTP to API Server</t>
-  </si>
-  <si>
-    <t>Missing Authentication covering communication link HTTP to API Server from Nginx Reverse Proxy to API Server</t>
-  </si>
-  <si>
-    <t>Authentication of Incoming Requests</t>
-  </si>
-  <si>
-    <t>Apply an authentication method to the technical asset. To protect highly sensitive data consider the use of two-factor authentication for human users.</t>
-  </si>
-  <si>
-    <t>missing-authentication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
-  </si>
-  <si>
-    <t>Unlikely</t>
-  </si>
-  <si>
-    <t>Very High</t>
-  </si>
-  <si>
-    <t>CWE-1008</t>
-  </si>
-  <si>
-    <t>Missing Cloud Hardening</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Missing Cloud Hardening risk at Docker Host</t>
-  </si>
-  <si>
-    <t>Cloud Hardening</t>
-  </si>
-  <si>
-    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
-  </si>
-  <si>
-    <t>missing-cloud-hardening@docker-host</t>
-  </si>
-  <si>
-    <t>CWE-693</t>
-  </si>
-  <si>
-    <t>Missing Content-Security-Policy Header on Web Entry Point</t>
+    <t>1</t>
   </si>
   <si>
     <t>Missing Content-Security-Policy: Nginx Reverse Proxy serves browser clients handling auth tokens without a verified CSP header</t>
@@ -293,7 +560,10 @@
     <t>Missing Hardening</t>
   </si>
   <si>
-    <t>Missing Hardening risk at API Server</t>
+    <t>AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at AWS RDS PostgreSQL</t>
   </si>
   <si>
     <t>System Hardening</t>
@@ -302,73 +572,157 @@
     <t>Try to apply all hardening best practices (like CIS benchmarks, OWASP recommendations, vendor recommendations, DevSec Hardening Framework, DBSAT for Oracle databases, and others).</t>
   </si>
   <si>
-    <t>missing-hardening@api-server</t>
-  </si>
-  <si>
-    <t>PostgreSQL Database</t>
+    <t>missing-hardening@rds-postgresql</t>
+  </si>
+  <si>
+    <t>ECS Container Platform</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
+    <t>Missing Hardening risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>missing-hardening@ecs-platform</t>
+  </si>
+  <si>
     <t>Missing Hardening risk at PostgreSQL Database</t>
   </si>
   <si>
     <t>missing-hardening@postgresql-db</t>
   </si>
   <si>
+    <t>CWE-22</t>
+  </si>
+  <si>
+    <t>Path-Traversal</t>
+  </si>
+  <si>
+    <t>MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal Prevention</t>
+  </si>
+  <si>
+    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at ECS Container Platform against filesystem AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>path-traversal@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Push Image to Registry</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at GitHub Actions Build Pipeline against filesystem AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>path-traversal@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>CWE-918</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF)</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>SSRF Prevention</t>
+  </si>
+  <si>
+    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>SES Email Send</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Lambda Email Notifier server-side web-requesting the target AWS SES via SES Email Send</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@lambda-notifier@aws-ses@lambda-notifier&gt;ses-email-send</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at ECS Container Platform server-side web-requesting the target AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at GitHub Actions Build Pipeline server-side web-requesting the target AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>Push to Pipeline</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at VaultNote Source Repository server-side web-requesting the target GitHub Actions Build Pipeline via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@source-repo@build-pipeline@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Redis Cache</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Missing Hardening risk at Redis Cache</t>
-  </si>
-  <si>
-    <t>missing-hardening@redis-cache</t>
-  </si>
-  <si>
-    <t>CWE-22</t>
-  </si>
-  <si>
-    <t>Path-Traversal</t>
-  </si>
-  <si>
-    <t>MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal Prevention</t>
-  </si>
-  <si>
-    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
-  </si>
-  <si>
-    <t>CWE-918</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF)</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>SSRF Prevention</t>
-  </si>
-  <si>
-    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+    <t>Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target Note RAG Pipeline via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@rag-pipeline@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>Query Vector Store</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target VaultNote Vector Store via Query Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@vector-store@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
+    <t>Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Note RAG Pipeline server-side web-requesting the target VaultNote Vector Store via Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@rag-pipeline@vector-store@rag-pipeline&gt;retrieve-from-vector-store</t>
   </si>
   <si>
     <t>CWE-319</t>
@@ -405,9 +759,6 @@
   </si>
   <si>
     <t>unencrypted-communication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t xml:space="preserve">Migrating Nginx-to-API communication to mTLS. A separate CA will be provisioned inside the Docker network. PR #47 is in review; target completion sprint 22.
@@ -417,15 +768,57 @@
     <t>2026-04-18</t>
   </si>
   <si>
-    <t>Security Team</t>
-  </si>
-  <si>
     <t>VAULT-102</t>
   </si>
   <si>
     <t>CWE-501</t>
   </si>
   <si>
+    <t>Unguarded Access From Internet</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of API Server by AWS API Gateway via Route to ECS API</t>
+  </si>
+  <si>
+    <t>Encapsulation of Technical Asset</t>
+  </si>
+  <si>
+    <t>Encapsulate the asset behind a guarding service, application, or reverse-proxy. For admin maintenance a bastion-host should be used as a jump-server. For file transfer a store-and-forward-host should be used as an indirect file exchange platform.</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@api-server@aws-api-gateway@aws-api-gateway&gt;route-to-ecs-api</t>
+  </si>
+  <si>
+    <t>AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of AWS ECR Container Registry by GitHub Actions Build Pipeline via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@container-registry@build-pipeline@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of GitHub Actions Build Pipeline by VaultNote Source Repository via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@build-pipeline@source-repo@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of Note RAG Pipeline by LLM Note Summarizer via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@rag-pipeline@llm-summarizer@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of VaultNote Vector Store by LLM Note Summarizer via Query Vector Store</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@vector-store@llm-summarizer@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access</t>
   </si>
   <si>
@@ -441,21 +834,66 @@
     <t>unguarded-direct-datastore-access@api-server&gt;postgresql-connection@api-server@postgresql-db</t>
   </si>
   <si>
+    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+  </si>
+  <si>
+    <t>Redis Cache</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access of Redis Cache by API Server via Redis Session Store</t>
   </si>
   <si>
     <t>unguarded-direct-datastore-access@api-server&gt;redis-session-store@api-server@redis-cache</t>
   </si>
   <si>
-    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+    <t>Accidental Secret Leak</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak(Git) risk at VaultNote Source Repository: Git Leak Prevention</t>
+  </si>
+  <si>
+    <t>Build Pipeline Hardening</t>
+  </si>
+  <si>
+    <t>Establish measures preventing accidental check-in or package-in of secrets into sourcecode repositories and artifact registries. This starts by using good .gitignore and .dockerignore files, but does not stop there. See for example tools like &lt;i&gt;\"git-secrets\"&lt;/i&gt; or &lt;i&gt;\"Talisman\"&lt;/i&gt; to have check-in preventive measures for secrets. Consider also to regularly scan your repositories for secrets accidentally checked-in using scanning tools like &lt;i&gt;"gitleaks"&lt;/i&gt; or &lt;i&gt;"gitrob"&lt;/i&gt;.</t>
+  </si>
+  <si>
+    <t>accidental-secret-leak@source-repo</t>
   </si>
   <si>
     <t>CWE-912</t>
   </si>
   <si>
+    <t>Code Backdooring</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>Reduce the attack surface of backdooring the build pipeline by not directly exposing the build pipeline components on the public internet and also not exposing it in front of unmanaged (out-of-scope) developer clients.Also consider the use of code signing to prevent code modifications.</t>
+  </si>
+  <si>
+    <t>code-backdooring@container-registry</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>code-backdooring@build-pipeline</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>code-backdooring@source-repo</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring</t>
   </si>
   <si>
@@ -492,12 +930,39 @@
     <t>container-baseimage-backdooring@minio-storage</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@rag-pipeline</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring risk at Redis Cache</t>
   </si>
   <si>
     <t>container-baseimage-backdooring@redis-cache</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@vector-store</t>
+  </si>
+  <si>
+    <t>Container Platform Escape</t>
+  </si>
+  <si>
+    <t>Container Platform Escape risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>Apply hardening of all container infrastructures. &lt;p&gt;See for example the &lt;i&gt;CIS-Benchmarks for Docker and Kubernetes&lt;/i&gt; as well as the &lt;i&gt;Docker Bench for Security&lt;/i&gt; ( &lt;a href="https://github.com/docker/docker-bench-security"&gt;https://github.com/docker/docker-bench-security&lt;/a&gt; ) or &lt;i&gt;InSpec Checks for Docker and Kubernetes&lt;/i&gt; ( &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-docker-benchmark&lt;/a&gt; and &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-kubernetes-benchmark&lt;/a&gt; ). Use only trusted base images, verify digital signatures and apply image creation best practices. Also consider using Google's &lt;b&gt;Distroless&lt;/i&gt; base images or otherwise very small base images. Apply namespace isolation and nod affinity to separate pods from each other in terms of access and nodes the same style as you separate data.</t>
+  </si>
+  <si>
+    <t>Are recommendations from the linked cheat sheet and referenced ASVS or CSVS chapter applied?</t>
+  </si>
+  <si>
+    <t>container-platform-escape@ecs-platform</t>
+  </si>
+  <si>
     <t>CWE-1127</t>
   </si>
   <si>
@@ -505,9 +970,6 @@
   </si>
   <si>
     <t>Missing Build Infrastructure in the threat model (referencing asset API Server as an example)</t>
-  </si>
-  <si>
-    <t>Build Pipeline Hardening</t>
   </si>
   <si>
     <t>Include the build infrastructure in the model.</t>
@@ -628,19 +1090,58 @@
     <t>VAULT-95</t>
   </si>
   <si>
+    <t>Unchecked Deployment</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Apply DevSecOps best-practices and use scanning tools to identify vulnerabilities in source- or byte-code,dependencies, container layers, and optionally also via dynamic scans against running test systems.</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@build-pipeline</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@source-repo</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@container-registry</t>
+  </si>
+  <si>
     <t>CWE-311</t>
   </si>
   <si>
     <t>Unencrypted Technical Assets</t>
   </si>
   <si>
+    <t>Unencrypted Technical Asset named AWS RDS PostgreSQL missing end user individual encryption with data-with-end-user-individual-key</t>
+  </si>
+  <si>
+    <t>Encryption of Technical Asset</t>
+  </si>
+  <si>
+    <t>Apply encryption to the technical asset.</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>Unencrypted Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@s3-notes-bucket</t>
+  </si>
+  <si>
     <t>Unencrypted Technical Asset named Redis Cache</t>
-  </si>
-  <si>
-    <t>Encryption of Technical Asset</t>
-  </si>
-  <si>
-    <t>Apply encryption to the technical asset.</t>
   </si>
   <si>
     <t>unencrypted-asset@redis-cache</t>
@@ -675,9 +1176,6 @@
     <t>VAULT-110</t>
   </si>
   <si>
-    <t>Denial of Service</t>
-  </si>
-  <si>
     <t>CWE-400</t>
   </si>
   <si>
@@ -709,6 +1207,27 @@
   </si>
   <si>
     <t>dos-risky-access-across-trust-boundary@postgresql-db@api-server@api-server&gt;postgresql-connection-&gt;</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>Attack Surface Reduction</t>
+  </si>
+  <si>
+    <t>Try to avoid using technical assets that do not process or store anything.</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@s3-notes-bucket</t>
   </si>
 </sst>
 </file>
@@ -1240,12 +1759,12 @@
     <col customWidth="true" max="4" min="4" width="25.57142857142857"/>
     <col customWidth="true" max="5" min="5" width="17.857142857142854"/>
     <col customWidth="true" max="6" min="6" width="13.571428571428571"/>
-    <col customWidth="true" max="7" min="7" width="55.57142857142857"/>
-    <col customWidth="true" max="8" min="8" width="23.857142857142858"/>
-    <col customWidth="true" max="9" min="9" width="25"/>
+    <col customWidth="true" max="7" min="7" width="73.57142857142857"/>
+    <col customWidth="true" max="8" min="8" width="31.57142857142857"/>
+    <col customWidth="true" max="9" min="9" width="29"/>
     <col customWidth="true" max="10" min="10" width="12"/>
     <col customWidth="true" max="11" min="11" width="75"/>
-    <col customWidth="true" max="12" min="12" width="66.42857142857143"/>
+    <col customWidth="true" max="12" min="12" width="84.28571428571429"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="14" min="14" width="40"/>
     <col customWidth="true" max="15" min="15" width="92.14285714285714"/>
@@ -1258,64 +1777,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="I1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="O1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>9</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">
@@ -1550,20 +2069,20 @@
       <c r="O5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>34</v>
+      <c r="P5" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1574,43 +2093,43 @@
         <v>52</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N6" s="23" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P6" s="10" t="s">
         <v>34</v>
@@ -1633,46 +2152,46 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>34</v>
@@ -1698,19 +2217,19 @@
         <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>57</v>
@@ -1722,34 +2241,34 @@
         <v>58</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>34</v>
+        <v>89</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -1763,40 +2282,40 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>34</v>
@@ -1822,120 +2341,120 @@
         <v>52</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>34</v>
+        <v>108</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="N11" s="23" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>34</v>
+        <v>117</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="S11" s="17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -1943,61 +2462,61 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="N12" s="23" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>34</v>
+        <v>127</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2008,43 +2527,43 @@
         <v>52</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>34</v>
@@ -2073,40 +2592,40 @@
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="N14" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>34</v>
@@ -2135,40 +2654,40 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="N15" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>34</v>
@@ -2191,46 +2710,46 @@
         <v>47</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="N16" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="P16" s="10" t="s">
         <v>34</v>
@@ -2253,108 +2772,108 @@
         <v>47</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="N17" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>128</v>
+        <v>159</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>40</v>
+      <c r="A18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="N18" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="P18" s="10" t="s">
         <v>34</v>
@@ -2383,40 +2902,40 @@
         <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="N19" s="23" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>34</v>
@@ -2435,50 +2954,50 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="7" t="s">
+      <c r="C20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>28</v>
-      </c>
       <c r="K20" s="19" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="M20" s="23" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="N20" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>34</v>
@@ -2497,50 +3016,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="7" t="s">
+      <c r="F21" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>34</v>
@@ -2559,50 +3078,50 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="A22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="7" t="s">
+      <c r="F22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="P22" s="10" t="s">
         <v>34</v>
@@ -2621,50 +3140,50 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>27</v>
+      <c r="A23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>34</v>
@@ -2683,50 +3202,50 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>27</v>
+      <c r="A24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="P24" s="10" t="s">
         <v>34</v>
@@ -2745,50 +3264,50 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>27</v>
+      <c r="A25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="N25" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>34</v>
@@ -2807,50 +3326,50 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="A26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>27</v>
+      <c r="I26" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="J26" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="N26" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="P26" s="10" t="s">
         <v>34</v>
@@ -2869,50 +3388,50 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>27</v>
+      <c r="A27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="N27" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>34</v>
@@ -2935,46 +3454,46 @@
         <v>48</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="P28" s="10" t="s">
         <v>34</v>
@@ -2997,7 +3516,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>48</v>
@@ -3006,37 +3525,37 @@
         <v>22</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>27</v>
+        <v>194</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="N29" s="23" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>34</v>
@@ -3059,46 +3578,46 @@
         <v>48</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>39</v>
+        <v>213</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>27</v>
+        <v>214</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N30" s="23" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>34</v>
@@ -3121,61 +3640,61 @@
         <v>48</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="N31" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>196</v>
+        <v>220</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>198</v>
+        <v>27</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -3183,46 +3702,46 @@
         <v>48</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F32" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L32" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="M32" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K32" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="L32" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="M32" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="N32" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>34</v>
@@ -3245,170 +3764,170 @@
         <v>48</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F33" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="L33" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="M33" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="L33" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="N33" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>196</v>
+        <v>226</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>211</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="A34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>27</v>
+      <c r="F34" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="N34" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O34" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="P34" s="12" t="s">
-        <v>128</v>
+        <v>232</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="R34" s="17" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="T34" s="16" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="A35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H35" s="9" t="s">
+      <c r="F35" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>219</v>
+      <c r="I35" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="J35" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="N35" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>34</v>
@@ -3427,50 +3946,50 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E36" s="10" t="s">
+      <c r="A36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>219</v>
+      <c r="F36" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="N36" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>34</v>
@@ -3489,69 +4008,2487 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E37" s="10" t="s">
+      <c r="A37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>40</v>
+      <c r="F37" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="M37" s="23" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="N37" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="P37" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q37" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="R37" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="S37" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="T37" s="16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N38" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="P38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="Q37" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R37" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S37" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T37" s="16" t="s">
+      <c r="Q38" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T41" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T42" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T44" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T45" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T47" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="L48" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q48" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T48" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T49" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T50" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T51" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O52" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T52" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="L53" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O53" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T53" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="L54" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O54" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T54" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="L55" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O55" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T55" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L56" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="O56" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q56" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T56" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="O57" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="L58" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O58" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T58" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="L59" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="N59" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O59" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T59" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="L60" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="N60" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O60" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="L61" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O61" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="L62" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="N62" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="O62" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T62" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="N63" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O63" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="P63" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q63" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="R63" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="S63" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="T63" s="16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="L64" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="N64" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O64" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T64" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="L65" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="N65" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O65" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q65" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="L66" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="N66" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O66" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="P66" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="L67" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O67" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q67" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="L68" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q68" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T68" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="K69" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="L69" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N69" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O69" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q69" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T69" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L70" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N70" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O70" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P70" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q70" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="R70" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="S70" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="T70" s="16" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="L71" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M71" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O71" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="P71" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q71" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="R71" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="S71" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="T71" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="J72" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O72" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q72" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T72" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="J73" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="L73" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="N73" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O73" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q73" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T73" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J74" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K74" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="L74" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="N74" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="P74" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q74" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R74" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S74" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T74" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K75" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="L75" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M75" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N75" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O75" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R75" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S75" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T75" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="L76" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N76" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O76" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q76" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T76" s="16" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$37"/>
+  <autoFilter ref="$A$1:$T$76"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>
